--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>54.7251</v>
+      </c>
+      <c r="C2">
+        <v>94.26518</v>
+      </c>
+      <c r="D2">
+        <v>79.90948</v>
+      </c>
+      <c r="E2">
+        <v>42.73156</v>
+      </c>
+      <c r="F2">
         <v>55.30264</v>
       </c>
-      <c r="C2">
-        <v>54.7251</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>100.6134</v>
       </c>
-      <c r="E2">
-        <v>94.26518</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>106.3906</v>
       </c>
-      <c r="G2">
-        <v>79.90948</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>66.47599</v>
-      </c>
-      <c r="I2">
-        <v>42.73156</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>63.50404</v>
+      </c>
+      <c r="C3">
+        <v>95.76591000000001</v>
+      </c>
+      <c r="D3">
+        <v>81.87372999999999</v>
+      </c>
+      <c r="E3">
+        <v>39.66172</v>
+      </c>
+      <c r="F3">
         <v>64.09704000000001</v>
       </c>
-      <c r="C3">
-        <v>63.50404</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>101.6179</v>
       </c>
-      <c r="E3">
-        <v>95.76591000000001</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>105.2953</v>
       </c>
-      <c r="G3">
-        <v>81.87372999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>55.81636</v>
-      </c>
-      <c r="I3">
-        <v>39.66172</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>53.29932</v>
+      </c>
+      <c r="C4">
+        <v>93.91152</v>
+      </c>
+      <c r="D4">
+        <v>81.94444</v>
+      </c>
+      <c r="E4">
+        <v>55.09406</v>
+      </c>
+      <c r="F4">
         <v>53.84354</v>
       </c>
-      <c r="C4">
-        <v>53.29932</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>98.70784</v>
       </c>
-      <c r="E4">
-        <v>93.91152</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>99.10131</v>
       </c>
-      <c r="G4">
-        <v>81.94444</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>72.09909</v>
-      </c>
-      <c r="I4">
-        <v>55.09406</v>
       </c>
     </row>
     <row r="5">
@@ -500,23 +500,23 @@
           <t>Juan Fernandez</t>
         </is>
       </c>
+      <c r="C5">
+        <v>96.7033</v>
+      </c>
       <c r="D5">
+        <v>79.48718</v>
+      </c>
+      <c r="E5">
+        <v>43.10345</v>
+      </c>
+      <c r="G5">
         <v>103.2967</v>
       </c>
-      <c r="E5">
-        <v>96.7033</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>94.87179999999999</v>
       </c>
-      <c r="G5">
-        <v>79.48718</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>67.24138000000001</v>
-      </c>
-      <c r="I5">
-        <v>43.10345</v>
       </c>
     </row>
     <row r="6">
@@ -526,28 +526,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>66.32577999999999</v>
+      </c>
+      <c r="C6">
+        <v>94.63303000000001</v>
+      </c>
+      <c r="D6">
+        <v>78.2235</v>
+      </c>
+      <c r="E6">
+        <v>40.20902</v>
+      </c>
+      <c r="F6">
         <v>66.54492</v>
       </c>
-      <c r="C6">
-        <v>66.32577999999999</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.1468</v>
       </c>
-      <c r="E6">
-        <v>94.63303000000001</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>100.7641</v>
       </c>
-      <c r="G6">
-        <v>78.2235</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>54.40044</v>
-      </c>
-      <c r="I6">
-        <v>40.20902</v>
       </c>
     </row>
     <row r="7">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>59.48196</v>
+      </c>
+      <c r="C7">
+        <v>95.86976</v>
+      </c>
+      <c r="D7">
+        <v>77.97102</v>
+      </c>
+      <c r="E7">
+        <v>36.88474</v>
+      </c>
+      <c r="F7">
         <v>59.9445</v>
       </c>
-      <c r="C7">
-        <v>59.48196</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>102.3214</v>
       </c>
-      <c r="E7">
-        <v>95.86976</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>102.3188</v>
       </c>
-      <c r="G7">
-        <v>77.97102</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>53.45794</v>
-      </c>
-      <c r="I7">
-        <v>36.88474</v>
       </c>
     </row>
     <row r="8">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>55.02971</v>
+      </c>
+      <c r="C8">
+        <v>94.35641</v>
+      </c>
+      <c r="D8">
+        <v>82.06647</v>
+      </c>
+      <c r="F8">
         <v>55.79687</v>
       </c>
-      <c r="C8">
-        <v>55.02971</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>99.59475999999999</v>
       </c>
-      <c r="E8">
-        <v>94.35641</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>105.9487</v>
-      </c>
-      <c r="G8">
-        <v>82.06647</v>
       </c>
     </row>
     <row r="9">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>53.75648</v>
+      </c>
+      <c r="C9">
+        <v>94.27083</v>
+      </c>
+      <c r="D9">
+        <v>77.80269</v>
+      </c>
+      <c r="E9">
+        <v>28.49807</v>
+      </c>
+      <c r="F9">
         <v>54.01554</v>
       </c>
-      <c r="C9">
-        <v>53.75648</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>100</v>
       </c>
-      <c r="E9">
-        <v>94.27083</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>94.61884000000001</v>
       </c>
-      <c r="G9">
-        <v>77.80269</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>43.6457</v>
-      </c>
-      <c r="I9">
-        <v>28.49807</v>
       </c>
     </row>
     <row r="10">
@@ -644,28 +644,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>58.17856</v>
+      </c>
+      <c r="C10">
+        <v>95.04311</v>
+      </c>
+      <c r="D10">
+        <v>84.68049999999999</v>
+      </c>
+      <c r="E10">
+        <v>40.23277</v>
+      </c>
+      <c r="F10">
         <v>58.51421</v>
       </c>
-      <c r="C10">
-        <v>58.17856</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.546</v>
       </c>
-      <c r="E10">
-        <v>95.04311</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>107.5915</v>
       </c>
-      <c r="G10">
-        <v>84.68049999999999</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>59.50271</v>
-      </c>
-      <c r="I10">
-        <v>40.23277</v>
       </c>
     </row>
     <row r="11">
@@ -675,28 +675,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>57.92039</v>
+      </c>
+      <c r="C11">
+        <v>96</v>
+      </c>
+      <c r="D11">
+        <v>84.03362</v>
+      </c>
+      <c r="E11">
+        <v>41.08216</v>
+      </c>
+      <c r="F11">
         <v>58.24533</v>
       </c>
-      <c r="C11">
-        <v>57.92039</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.9444</v>
       </c>
-      <c r="E11">
-        <v>96</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>106.3625</v>
       </c>
-      <c r="G11">
-        <v>84.03362</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>54.50902</v>
-      </c>
-      <c r="I11">
-        <v>41.08216</v>
       </c>
     </row>
     <row r="12">
@@ -706,28 +706,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>62.48447</v>
+      </c>
+      <c r="C12">
+        <v>96.00626</v>
+      </c>
+      <c r="D12">
+        <v>83.5034</v>
+      </c>
+      <c r="E12">
+        <v>40.18265</v>
+      </c>
+      <c r="F12">
         <v>62.85714</v>
       </c>
-      <c r="C12">
-        <v>62.48447</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>100.1566</v>
       </c>
-      <c r="E12">
-        <v>96.00626</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>112.9252</v>
       </c>
-      <c r="G12">
-        <v>83.5034</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>57.99087</v>
-      </c>
-      <c r="I12">
-        <v>40.18265</v>
       </c>
     </row>
     <row r="13">
@@ -737,28 +737,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>58.43465</v>
+      </c>
+      <c r="C13">
+        <v>96.30840999999999</v>
+      </c>
+      <c r="D13">
+        <v>87.86982</v>
+      </c>
+      <c r="E13">
+        <v>39.61814</v>
+      </c>
+      <c r="F13">
         <v>58.81459</v>
       </c>
-      <c r="C13">
-        <v>58.43465</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>100.9346</v>
       </c>
-      <c r="E13">
-        <v>96.30840999999999</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>109.6647</v>
       </c>
-      <c r="G13">
-        <v>87.86982</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>56.27685</v>
-      </c>
-      <c r="I13">
-        <v>39.61814</v>
       </c>
     </row>
     <row r="14">
@@ -768,28 +768,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>61.21383</v>
+      </c>
+      <c r="C14">
+        <v>96.28548000000001</v>
+      </c>
+      <c r="D14">
+        <v>87.82117</v>
+      </c>
+      <c r="E14">
+        <v>40.52974</v>
+      </c>
+      <c r="F14">
         <v>61.3746</v>
       </c>
-      <c r="C14">
-        <v>61.21383</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>100.2653</v>
       </c>
-      <c r="E14">
-        <v>96.28548000000001</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>104.8304</v>
       </c>
-      <c r="G14">
-        <v>87.82117</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>56.67167</v>
-      </c>
-      <c r="I14">
-        <v>40.52974</v>
       </c>
     </row>
     <row r="15">
@@ -799,28 +799,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>57.28953</v>
+      </c>
+      <c r="C15">
+        <v>97.34815999999999</v>
+      </c>
+      <c r="D15">
+        <v>88.19672</v>
+      </c>
+      <c r="E15">
+        <v>36.70732</v>
+      </c>
+      <c r="F15">
         <v>57.90554</v>
       </c>
-      <c r="C15">
-        <v>57.28953</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>100.7699</v>
       </c>
-      <c r="E15">
-        <v>97.34815999999999</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>107.1311</v>
       </c>
-      <c r="G15">
-        <v>88.19672</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>49.10569</v>
-      </c>
-      <c r="I15">
-        <v>36.70732</v>
       </c>
     </row>
     <row r="16">
@@ -830,28 +830,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>65.59139</v>
+      </c>
+      <c r="C16">
+        <v>94.76439999999999</v>
+      </c>
+      <c r="D16">
+        <v>87.17104999999999</v>
+      </c>
+      <c r="E16">
+        <v>40.37267</v>
+      </c>
+      <c r="F16">
         <v>65.86021</v>
       </c>
-      <c r="C16">
-        <v>65.59139</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>97.73124</v>
       </c>
-      <c r="E16">
-        <v>94.76439999999999</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>104.6053</v>
       </c>
-      <c r="G16">
-        <v>87.17104999999999</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>51.39751</v>
-      </c>
-      <c r="I16">
-        <v>40.37267</v>
       </c>
     </row>
     <row r="17">
@@ -861,28 +861,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>59.81013</v>
+      </c>
+      <c r="C17">
+        <v>96.30709</v>
+      </c>
+      <c r="D17">
+        <v>88.99804</v>
+      </c>
+      <c r="E17">
+        <v>41.26163</v>
+      </c>
+      <c r="F17">
         <v>60.12658</v>
       </c>
-      <c r="C17">
-        <v>59.81013</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>99.02818000000001</v>
       </c>
-      <c r="E17">
-        <v>96.30709</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>100.9823</v>
       </c>
-      <c r="G17">
-        <v>88.99804</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>56.04964</v>
-      </c>
-      <c r="I17">
-        <v>41.26163</v>
       </c>
     </row>
     <row r="18">
@@ -892,28 +892,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>67.22221999999999</v>
+      </c>
+      <c r="C18">
+        <v>93.40974</v>
+      </c>
+      <c r="D18">
+        <v>86.01582999999999</v>
+      </c>
+      <c r="E18">
+        <v>41.67585</v>
+      </c>
+      <c r="F18">
         <v>67.40741</v>
       </c>
-      <c r="C18">
-        <v>67.22221999999999</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>96.56161</v>
       </c>
-      <c r="E18">
-        <v>93.40974</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>102.1108</v>
       </c>
-      <c r="G18">
-        <v>86.01582999999999</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>53.80375</v>
-      </c>
-      <c r="I18">
-        <v>41.67585</v>
       </c>
     </row>
     <row r="19">
@@ -923,28 +923,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>61.8679</v>
+      </c>
+      <c r="C19">
+        <v>94.95281</v>
+      </c>
+      <c r="D19">
+        <v>79.15401</v>
+      </c>
+      <c r="E19">
+        <v>41.02163</v>
+      </c>
+      <c r="F19">
         <v>62.4871</v>
       </c>
-      <c r="C19">
-        <v>61.8679</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>101.5057</v>
       </c>
-      <c r="E19">
-        <v>94.95281</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>103.2787</v>
       </c>
-      <c r="G19">
-        <v>79.15401</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>61.74773</v>
-      </c>
-      <c r="I19">
-        <v>41.02163</v>
       </c>
     </row>
     <row r="20">
@@ -954,28 +954,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>63.25661</v>
+      </c>
+      <c r="C20">
+        <v>95.94167</v>
+      </c>
+      <c r="D20">
+        <v>82.14286</v>
+      </c>
+      <c r="E20">
+        <v>39.62892</v>
+      </c>
+      <c r="F20">
         <v>63.34186</v>
       </c>
-      <c r="C20">
-        <v>63.25661</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>101.0365</v>
       </c>
-      <c r="E20">
-        <v>95.94167</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>110.4978</v>
       </c>
-      <c r="G20">
-        <v>82.14286</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>56.4327</v>
-      </c>
-      <c r="I20">
-        <v>39.62892</v>
       </c>
     </row>
     <row r="21">
@@ -985,28 +985,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>60.79193</v>
+      </c>
+      <c r="C21">
+        <v>96.11084</v>
+      </c>
+      <c r="D21">
+        <v>79.87072999999999</v>
+      </c>
+      <c r="E21">
+        <v>34.53202</v>
+      </c>
+      <c r="F21">
         <v>61.25776</v>
       </c>
-      <c r="C21">
-        <v>60.79193</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>102.3335</v>
       </c>
-      <c r="E21">
-        <v>96.11084</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>98.52262</v>
       </c>
-      <c r="G21">
-        <v>79.87072999999999</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>47.04433</v>
-      </c>
-      <c r="I21">
-        <v>34.53202</v>
       </c>
     </row>
     <row r="22">
@@ -1016,28 +1016,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>60.64442</v>
+      </c>
+      <c r="C22">
+        <v>95.68867</v>
+      </c>
+      <c r="D22">
+        <v>82.80508</v>
+      </c>
+      <c r="E22">
+        <v>51.75601</v>
+      </c>
+      <c r="F22">
         <v>60.75949</v>
       </c>
-      <c r="C22">
-        <v>60.64442</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>101.2591</v>
       </c>
-      <c r="E22">
-        <v>95.68867</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>101.9017</v>
       </c>
-      <c r="G22">
-        <v>82.80508</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>76.98706</v>
-      </c>
-      <c r="I22">
-        <v>51.75601</v>
       </c>
     </row>
     <row r="23">
@@ -1047,28 +1047,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>62.88874</v>
+      </c>
+      <c r="C23">
+        <v>96.52956</v>
+      </c>
+      <c r="D23">
+        <v>85.25122</v>
+      </c>
+      <c r="E23">
+        <v>38.91978</v>
+      </c>
+      <c r="F23">
         <v>63.09606</v>
       </c>
-      <c r="C23">
-        <v>62.88874</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>102.1422</v>
       </c>
-      <c r="E23">
-        <v>96.52956</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>107.6175</v>
       </c>
-      <c r="G23">
-        <v>85.25122</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>53.01827</v>
-      </c>
-      <c r="I23">
-        <v>38.91978</v>
       </c>
     </row>
     <row r="24">
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>61.21222</v>
+      </c>
+      <c r="C24">
+        <v>95.07323</v>
+      </c>
+      <c r="D24">
+        <v>82.20027</v>
+      </c>
+      <c r="E24">
+        <v>38.7188</v>
+      </c>
+      <c r="F24">
         <v>61.63471</v>
       </c>
-      <c r="C24">
-        <v>61.21222</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>100.3138</v>
       </c>
-      <c r="E24">
-        <v>95.07323</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>105.307</v>
       </c>
-      <c r="G24">
-        <v>82.20027</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>56.44135</v>
-      </c>
-      <c r="I24">
-        <v>38.7188</v>
       </c>
     </row>
     <row r="25">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>52.81474</v>
+      </c>
+      <c r="C25">
+        <v>93.95218</v>
+      </c>
+      <c r="D25">
+        <v>80.02853</v>
+      </c>
+      <c r="E25">
+        <v>40.25788</v>
+      </c>
+      <c r="F25">
         <v>53.01945</v>
       </c>
-      <c r="C25">
-        <v>52.81474</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>98.66386</v>
       </c>
-      <c r="E25">
-        <v>93.95218</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>100.1427</v>
       </c>
-      <c r="G25">
-        <v>80.02853</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>54.51289</v>
-      </c>
-      <c r="I25">
-        <v>40.25788</v>
       </c>
     </row>
     <row r="26">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>60.25237</v>
+      </c>
+      <c r="C26">
+        <v>95.45278999999999</v>
+      </c>
+      <c r="D26">
+        <v>78.05970000000001</v>
+      </c>
+      <c r="E26">
+        <v>34.51586</v>
+      </c>
+      <c r="F26">
         <v>60.82019</v>
       </c>
-      <c r="C26">
-        <v>60.25237</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>101.5029</v>
       </c>
-      <c r="E26">
-        <v>95.45278999999999</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>106.194</v>
       </c>
-      <c r="G26">
-        <v>78.05970000000001</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>48.24708</v>
-      </c>
-      <c r="I26">
-        <v>34.51586</v>
       </c>
     </row>
     <row r="27">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>52.76243</v>
+      </c>
+      <c r="C27">
+        <v>90.95808</v>
+      </c>
+      <c r="D27">
+        <v>81.32004999999999</v>
+      </c>
+      <c r="E27">
+        <v>35</v>
+      </c>
+      <c r="F27">
         <v>52.94659</v>
       </c>
-      <c r="C27">
-        <v>52.76243</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>94.91018</v>
       </c>
-      <c r="E27">
-        <v>90.95808</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>102.8643</v>
       </c>
-      <c r="G27">
-        <v>81.32004999999999</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>48.94737</v>
-      </c>
-      <c r="I27">
-        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -1205,25 +1205,25 @@
         <v>57.09534</v>
       </c>
       <c r="C28">
+        <v>93.60731</v>
+      </c>
+      <c r="D28">
+        <v>79.03225999999999</v>
+      </c>
+      <c r="E28">
+        <v>36.19303</v>
+      </c>
+      <c r="F28">
         <v>57.09534</v>
       </c>
-      <c r="D28">
+      <c r="G28">
         <v>98.93455</v>
       </c>
-      <c r="E28">
-        <v>93.60731</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>107.7419</v>
       </c>
-      <c r="G28">
-        <v>79.03225999999999</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>51.38517</v>
-      </c>
-      <c r="I28">
-        <v>36.19303</v>
       </c>
     </row>
     <row r="29">
@@ -1233,28 +1233,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>63.03192</v>
+      </c>
+      <c r="C29">
+        <v>94.76351</v>
+      </c>
+      <c r="D29">
+        <v>84.46455</v>
+      </c>
+      <c r="E29">
+        <v>50.54576</v>
+      </c>
+      <c r="F29">
         <v>63.29787</v>
       </c>
-      <c r="C29">
-        <v>63.03192</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>98.64865</v>
       </c>
-      <c r="E29">
-        <v>94.76351</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>102.5641</v>
       </c>
-      <c r="G29">
-        <v>84.46455</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>69.26952</v>
-      </c>
-      <c r="I29">
-        <v>50.54576</v>
       </c>
     </row>
     <row r="30">
@@ -1264,28 +1264,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>61.20704</v>
+      </c>
+      <c r="C30">
+        <v>95.52675000000001</v>
+      </c>
+      <c r="D30">
+        <v>82.31555</v>
+      </c>
+      <c r="E30">
+        <v>40.91184</v>
+      </c>
+      <c r="F30">
         <v>62.13152</v>
       </c>
-      <c r="C30">
-        <v>61.20704</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>100.7358</v>
       </c>
-      <c r="E30">
-        <v>95.52675000000001</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>103.8593</v>
       </c>
-      <c r="G30">
-        <v>82.31555</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>56.94977</v>
-      </c>
-      <c r="I30">
-        <v>40.91184</v>
       </c>
     </row>
     <row r="31">
@@ -1295,28 +1295,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>68.86792</v>
+      </c>
+      <c r="C31">
+        <v>96.11147</v>
+      </c>
+      <c r="D31">
+        <v>84.2953</v>
+      </c>
+      <c r="E31">
+        <v>35.92617</v>
+      </c>
+      <c r="F31">
         <v>69.28721</v>
       </c>
-      <c r="C31">
-        <v>68.86792</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>103.1756</v>
       </c>
-      <c r="E31">
-        <v>96.11147</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>117.8523</v>
       </c>
-      <c r="G31">
-        <v>84.2953</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>48.58273</v>
-      </c>
-      <c r="I31">
-        <v>35.92617</v>
       </c>
     </row>
     <row r="32">
@@ -1326,28 +1326,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>67.16343999999999</v>
+      </c>
+      <c r="C32">
+        <v>95.78873</v>
+      </c>
+      <c r="D32">
+        <v>84.36620000000001</v>
+      </c>
+      <c r="E32">
+        <v>40.05979</v>
+      </c>
+      <c r="F32">
         <v>67.70988</v>
       </c>
-      <c r="C32">
-        <v>67.16343999999999</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>102.7837</v>
       </c>
-      <c r="E32">
-        <v>95.78873</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>113.8732</v>
       </c>
-      <c r="G32">
-        <v>84.36620000000001</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>58.52018</v>
-      </c>
-      <c r="I32">
-        <v>40.05979</v>
       </c>
     </row>
     <row r="33">
@@ -1360,25 +1360,25 @@
         <v>71.11111</v>
       </c>
       <c r="C33">
+        <v>97.59798000000001</v>
+      </c>
+      <c r="D33">
+        <v>86.30137000000001</v>
+      </c>
+      <c r="E33">
+        <v>36.69623</v>
+      </c>
+      <c r="F33">
         <v>71.11111</v>
       </c>
-      <c r="D33">
+      <c r="G33">
         <v>102.2756</v>
       </c>
-      <c r="E33">
-        <v>97.59798000000001</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>107.3059</v>
       </c>
-      <c r="G33">
-        <v>86.30137000000001</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>53.43681</v>
-      </c>
-      <c r="I33">
-        <v>36.69623</v>
       </c>
     </row>
     <row r="34">
@@ -1388,28 +1388,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>65.44240000000001</v>
+      </c>
+      <c r="C34">
+        <v>95.93496</v>
+      </c>
+      <c r="D34">
+        <v>84.7619</v>
+      </c>
+      <c r="E34">
+        <v>37.39362</v>
+      </c>
+      <c r="F34">
         <v>65.85975999999999</v>
       </c>
-      <c r="C34">
-        <v>65.44240000000001</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>102.3229</v>
       </c>
-      <c r="E34">
-        <v>95.93496</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>117.7778</v>
       </c>
-      <c r="G34">
-        <v>84.7619</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>53.08511</v>
-      </c>
-      <c r="I34">
-        <v>37.39362</v>
       </c>
     </row>
     <row r="35">
@@ -1419,28 +1419,28 @@
         </is>
       </c>
       <c r="B35">
+        <v>72.40076000000001</v>
+      </c>
+      <c r="C35">
+        <v>96.85574</v>
+      </c>
+      <c r="D35">
+        <v>82.3147</v>
+      </c>
+      <c r="E35">
+        <v>36.69891</v>
+      </c>
+      <c r="F35">
         <v>72.77883</v>
       </c>
-      <c r="C35">
-        <v>72.40076000000001</v>
-      </c>
-      <c r="D35">
+      <c r="G35">
         <v>101.8496</v>
       </c>
-      <c r="E35">
-        <v>96.85574</v>
-      </c>
-      <c r="F35">
+      <c r="H35">
         <v>107.1521</v>
       </c>
-      <c r="G35">
-        <v>82.3147</v>
-      </c>
-      <c r="H35">
+      <c r="I35">
         <v>52.47884</v>
-      </c>
-      <c r="I35">
-        <v>36.69891</v>
       </c>
     </row>
     <row r="36">
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="B36">
+        <v>58.69105</v>
+      </c>
+      <c r="C36">
+        <v>94.89037</v>
+      </c>
+      <c r="D36">
+        <v>82.47423000000001</v>
+      </c>
+      <c r="E36">
+        <v>49.59566</v>
+      </c>
+      <c r="F36">
         <v>59.11473</v>
       </c>
-      <c r="C36">
-        <v>58.69105</v>
-      </c>
-      <c r="D36">
+      <c r="G36">
         <v>100.6773</v>
       </c>
-      <c r="E36">
-        <v>94.89037</v>
-      </c>
-      <c r="F36">
+      <c r="H36">
         <v>106.8689</v>
       </c>
-      <c r="G36">
-        <v>82.47423000000001</v>
-      </c>
-      <c r="H36">
+      <c r="I36">
         <v>73.90355</v>
-      </c>
-      <c r="I36">
-        <v>49.59566</v>
       </c>
     </row>
     <row r="37">
@@ -1481,28 +1481,28 @@
         </is>
       </c>
       <c r="B37">
+        <v>57.3548</v>
+      </c>
+      <c r="C37">
+        <v>93.17435</v>
+      </c>
+      <c r="D37">
+        <v>79.82456000000001</v>
+      </c>
+      <c r="E37">
+        <v>40.59288</v>
+      </c>
+      <c r="F37">
         <v>57.57576</v>
       </c>
-      <c r="C37">
-        <v>57.3548</v>
-      </c>
-      <c r="D37">
+      <c r="G37">
         <v>98.74589</v>
       </c>
-      <c r="E37">
-        <v>93.17435</v>
-      </c>
-      <c r="F37">
+      <c r="H37">
         <v>108.8118</v>
       </c>
-      <c r="G37">
-        <v>79.82456000000001</v>
-      </c>
-      <c r="H37">
+      <c r="I37">
         <v>59.90118</v>
-      </c>
-      <c r="I37">
-        <v>40.59288</v>
       </c>
     </row>
     <row r="38">
@@ -1512,28 +1512,28 @@
         </is>
       </c>
       <c r="B38">
+        <v>56.31068</v>
+      </c>
+      <c r="C38">
+        <v>93.64035</v>
+      </c>
+      <c r="D38">
+        <v>80.21277000000001</v>
+      </c>
+      <c r="E38">
+        <v>35.88907</v>
+      </c>
+      <c r="F38">
         <v>56.71521</v>
       </c>
-      <c r="C38">
-        <v>56.31068</v>
-      </c>
-      <c r="D38">
+      <c r="G38">
         <v>99.01316</v>
       </c>
-      <c r="E38">
-        <v>93.64035</v>
-      </c>
-      <c r="F38">
+      <c r="H38">
         <v>103.617</v>
       </c>
-      <c r="G38">
-        <v>80.21277000000001</v>
-      </c>
-      <c r="H38">
+      <c r="I38">
         <v>52.31104</v>
-      </c>
-      <c r="I38">
-        <v>35.88907</v>
       </c>
     </row>
     <row r="39">
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="B39">
+        <v>59.85988</v>
+      </c>
+      <c r="C39">
+        <v>94.96079</v>
+      </c>
+      <c r="D39">
+        <v>81.71495</v>
+      </c>
+      <c r="E39">
+        <v>48.80603</v>
+      </c>
+      <c r="F39">
         <v>60.31396</v>
       </c>
-      <c r="C39">
-        <v>59.85988</v>
-      </c>
-      <c r="D39">
+      <c r="G39">
         <v>100.3339</v>
       </c>
-      <c r="E39">
-        <v>94.96079</v>
-      </c>
-      <c r="F39">
+      <c r="H39">
         <v>105.5612</v>
       </c>
-      <c r="G39">
-        <v>81.71495</v>
-      </c>
-      <c r="H39">
+      <c r="I39">
         <v>72.17326</v>
-      </c>
-      <c r="I39">
-        <v>48.80603</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:47</t>
+    <t xml:space="preserve">2026-08-03 09:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 09:35</t>
+    <t xml:space="preserve">2026-08-05 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:35</t>
+    <t xml:space="preserve">2026-08-16 09:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:47</t>
+    <t xml:space="preserve">2026-08-19 12:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:00</t>
+    <t xml:space="preserve">2026-08-28 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:26</t>
+    <t xml:space="preserve">2026-09-06 17:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
